--- a/app/reports/SNYR_research.xlsx
+++ b/app/reports/SNYR_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-25 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-26 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.2038</v>
+        <v>0.2117</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04383999824523926</v>
+        <v>0.04372000217437744</v>
       </c>
     </row>
     <row r="6">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>14899882.23748773</v>
+        <v>14899881.90836089</v>
       </c>
     </row>
     <row r="36">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>0.2038</v>
+        <v>0.2117</v>
       </c>
     </row>
     <row r="38">
@@ -1497,11 +1497,11 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>3036596</v>
+        <v>3154305</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>-2.82</v>
+        <v>-2.81</v>
       </c>
       <c r="F5" s="31" t="n">
         <v>1.1</v>
@@ -1519,11 +1519,11 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>14414588</v>
+        <v>14558956</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n">
-        <v>-1.341</v>
+        <v>-1.331</v>
       </c>
       <c r="F6" s="33" t="n"/>
     </row>
@@ -1539,12 +1539,12 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>20206620</v>
+        <v>20683940</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n"/>
       <c r="F7" s="33" t="n">
-        <v>64.83499999999999</v>
+        <v>63.451</v>
       </c>
     </row>
     <row r="8">
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>64786064</v>
+        <v>66003668</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>-1.919</v>
+        <v>-1.891</v>
       </c>
       <c r="F8" s="33" t="n"/>
     </row>
@@ -1595,14 +1595,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>52459080</v>
+        <v>54815928</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-1.067</v>
+        <v>-1.21</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>103.172</v>
+        <v>116.971</v>
       </c>
     </row>
     <row r="11">
@@ -1617,14 +1617,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>15709928</v>
+        <v>14735595</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.413</v>
+        <v>-1.474</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>659.313</v>
+        <v>687.458</v>
       </c>
     </row>
     <row r="12">
@@ -1639,14 +1639,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>7129959</v>
+        <v>7666321</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>-0.494</v>
+        <v>-0.509</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>15.176</v>
+        <v>15.654</v>
       </c>
     </row>
     <row r="13">
@@ -1661,11 +1661,11 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>5382992</v>
+        <v>5342301</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-0.25</v>
+        <v>-0.242</v>
       </c>
       <c r="F13" s="33" t="n"/>
     </row>

--- a/app/reports/SNYR_research.xlsx
+++ b/app/reports/SNYR_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-26 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-27 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.2117</v>
+        <v>0.2092</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04372</v>
       </c>
     </row>
     <row r="6">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>14899881.90836089</v>
+        <v>14899880.49713193</v>
       </c>
     </row>
     <row r="36">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>0.2117</v>
+        <v>0.2092</v>
       </c>
     </row>
     <row r="38">
@@ -1497,11 +1497,11 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>3154305</v>
+        <v>3117055</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>-2.81</v>
+        <v>-2.82</v>
       </c>
       <c r="F5" s="31" t="n">
         <v>1.1</v>
@@ -1519,11 +1519,11 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>14558956</v>
+        <v>14343515</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n">
-        <v>-1.331</v>
+        <v>-1.359</v>
       </c>
       <c r="F6" s="33" t="n"/>
     </row>
@@ -1544,7 +1544,7 @@
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n"/>
       <c r="F7" s="33" t="n">
-        <v>63.451</v>
+        <v>64.83499999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>66003668</v>
+        <v>66806420</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>-1.891</v>
+        <v>-2.003</v>
       </c>
       <c r="F8" s="33" t="n"/>
     </row>
@@ -1595,14 +1595,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>54815928</v>
+        <v>51334568</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-1.21</v>
+        <v>-1.188</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>116.971</v>
+        <v>114.869</v>
       </c>
     </row>
     <row r="11">
@@ -1617,14 +1617,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>14735595</v>
+        <v>14553787</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.474</v>
+        <v>-1.311</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>687.458</v>
+        <v>611.684</v>
       </c>
     </row>
     <row r="12">
@@ -1639,14 +1639,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>7666321</v>
+        <v>7646935</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>-0.509</v>
+        <v>-0.543</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>15.654</v>
+        <v>16.685</v>
       </c>
     </row>
     <row r="13">
@@ -1661,11 +1661,11 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>5342301</v>
+        <v>5148539</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-0.242</v>
+        <v>-0.237</v>
       </c>
       <c r="F13" s="33" t="n"/>
     </row>

--- a/app/reports/SNYR_research.xlsx
+++ b/app/reports/SNYR_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-27 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-28 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04372</v>
+        <v>0.04372000217437744</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/SNYR_research.xlsx
+++ b/app/reports/SNYR_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-28 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.2092</v>
+        <v>0.2149</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04375999927520752</v>
       </c>
     </row>
     <row r="6">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>14899880.49713193</v>
+        <v>14899883.66682178</v>
       </c>
     </row>
     <row r="36">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>0.2092</v>
+        <v>0.2149</v>
       </c>
     </row>
     <row r="38">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>3117055</v>
+        <v>3201985</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>14343515</v>
+        <v>15103113</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>20683940</v>
+        <v>20513696</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n"/>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>66806420</v>
+        <v>71116512</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>51334568</v>
+        <v>53837756</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>14553787</v>
+        <v>14599126</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>7646935</v>
+        <v>7541386</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>5148539</v>
+        <v>5453023</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
